--- a/artfynd/A 15353-2020 artfynd.xlsx
+++ b/artfynd/A 15353-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 15353-2020 artfynd.xlsx
+++ b/artfynd/A 15353-2020 artfynd.xlsx
@@ -9396,7 +9396,7 @@
         <v>121300256</v>
       </c>
       <c r="B66" t="n">
-        <v>6664</v>
+        <v>6667</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>

--- a/artfynd/A 15353-2020 artfynd.xlsx
+++ b/artfynd/A 15353-2020 artfynd.xlsx
@@ -9396,7 +9396,7 @@
         <v>121300256</v>
       </c>
       <c r="B66" t="n">
-        <v>6667</v>
+        <v>6668</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>

--- a/artfynd/A 15353-2020 artfynd.xlsx
+++ b/artfynd/A 15353-2020 artfynd.xlsx
@@ -9970,7 +9970,7 @@
         <v>126728120</v>
       </c>
       <c r="B71" t="n">
-        <v>80296</v>
+        <v>80327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
